--- a/quizzes/018_weekdays_knowledge_quiz--quizzes.xlsx
+++ b/quizzes/018_weekdays_knowledge_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>week_days_1</t>
+          <t>select_weekday_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Weekdays</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Best Weekday</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Select the best weekday</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>score_1</t>
+          <t>score_monday_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Score for Monday</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter a score for Monday</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>score_2</t>
+          <t>score_tuesday_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Score for Tuesday</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter a score for Tuesday</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +601,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>score_3</t>
+          <t>score_wednesday_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Score for Wednesday</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter a score for Wednesday</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>score_4</t>
+          <t>score_thursday_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Score for Thursday</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter a score for Thursday</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>score_5</t>
+          <t>score_friday_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Score for Friday</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter a score for Friday</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,7 +682,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -666,10 +690,14 @@
           <t>Comments</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter comments for the week</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,7 +709,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -689,10 +717,14 @@
           <t>Submitted By</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select the person who submitted</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -710,7 +742,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -735,7 +767,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>week_days_1_choices</t>
+          <t>select_weekday_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -752,7 +784,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>week_days_1_choices</t>
+          <t>select_weekday_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -769,7 +801,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>week_days_1_choices</t>
+          <t>select_weekday_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -786,7 +818,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>week_days_1_choices</t>
+          <t>select_weekday_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -803,7 +835,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>week_days_1_choices</t>
+          <t>select_weekday_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -820,7 +852,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>week_days_1_choices</t>
+          <t>select_weekday_1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -837,7 +869,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>week_days_1_choices</t>
+          <t>select_weekday_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -854,7 +886,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -871,7 +903,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -888,7 +920,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_1_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
